--- a/nriss-patch-2/ig/StructureDefinition-fr-related-person-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-related-person-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="458">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -684,7 +684,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -753,7 +753,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:Role.id</t>
@@ -1024,41 +1024,34 @@
     <t>Nom de la personne</t>
   </si>
   <si>
-    <t>A human's name with the ability to identify parts and usage.</t>
-  </si>
-  <si>
-    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
+    <t>A name associated with the person.</t>
   </si>
   <si>
     <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
+    <t>name</t>
+  </si>
+  <si>
+    <t>NK1-2</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name.extension:assemblyOrder</t>
+  </si>
+  <si>
+    <t>assemblyOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
 </t>
   </si>
   <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>XPN</t>
-  </si>
-  <si>
-    <t>RelatedPerson.name.id</t>
-  </si>
-  <si>
-    <t>RelatedPerson.name.extension</t>
-  </si>
-  <si>
-    <t>RelatedPerson.name.extension:assemblyOrder</t>
-  </si>
-  <si>
-    <t>assemblyOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0}
-</t>
-  </si>
-  <si>
     <t>Preferred display order of name parts</t>
   </si>
   <si>
@@ -1078,6 +1071,9 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
@@ -1236,14 +1232,14 @@
     <t>RelatedPerson.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>A contact detail for the person</t>
+  </si>
+  <si>
+    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
   </si>
   <si>
     <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
@@ -1252,14 +1248,10 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
-    <t>XTN</t>
+    <t>telecom</t>
+  </si>
+  <si>
+    <t>NK1-5 / NK1-6 / NK1-40</t>
   </si>
   <si>
     <t>RelatedPerson.gender</t>
@@ -1305,26 +1297,23 @@
     <t>RelatedPerson.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.1.0}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>Address where the related person can be contacted or visited</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited.</t>
   </si>
   <si>
     <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
   </si>
   <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>XAD</t>
+    <t>addr</t>
+  </si>
+  <si>
+    <t>NK1-4</t>
   </si>
   <si>
     <t>RelatedPerson.photo</t>
@@ -7045,7 +7034,7 @@
         <v>76</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>323</v>
@@ -7056,11 +7045,9 @@
       <c r="M48" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7118,27 +7105,27 @@
         <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7244,10 +7231,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7355,13 +7342,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>76</v>
@@ -7383,13 +7370,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7466,10 +7453,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7495,16 +7482,16 @@
         <v>165</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7531,27 +7518,29 @@
       <c r="X52" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="Y52" s="2"/>
+      <c r="Y52" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="Z52" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7566,21 +7555,21 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7606,16 +7595,16 @@
         <v>99</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7664,7 +7653,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7679,25 +7668,25 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>354</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7719,13 +7708,13 @@
         <v>99</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7775,7 +7764,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7790,25 +7779,25 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7830,13 +7819,13 @@
         <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7886,7 +7875,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7901,21 +7890,21 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>370</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7941,10 +7930,10 @@
         <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7975,25 +7964,25 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8008,21 +7997,21 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>377</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8048,10 +8037,10 @@
         <v>99</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8082,25 +8071,25 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8115,21 +8104,21 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8152,17 +8141,17 @@
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8211,7 +8200,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8226,21 +8215,21 @@
         <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8260,22 +8249,22 @@
         <v>76</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8324,7 +8313,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8333,27 +8322,27 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8379,14 +8368,14 @@
         <v>165</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8414,10 +8403,10 @@
         <v>308</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
@@ -8435,7 +8424,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8450,21 +8439,21 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8487,13 +8476,13 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8544,7 +8533,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8559,7 +8548,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8570,10 +8559,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8593,22 +8582,20 @@
         <v>76</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>76</v>
@@ -8657,7 +8644,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8666,27 +8653,27 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8709,17 +8696,17 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8768,7 +8755,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8783,21 +8770,21 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8820,13 +8807,13 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8877,7 +8864,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8892,10 +8879,10 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8903,10 +8890,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8929,19 +8916,19 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8990,7 +8977,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9005,7 +8992,7 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -9016,10 +9003,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9125,10 +9112,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9236,14 +9223,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9265,10 +9252,10 @@
         <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>109</v>
@@ -9323,7 +9310,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9349,10 +9336,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9378,16 +9365,16 @@
         <v>222</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9436,7 +9423,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>85</v>
@@ -9451,7 +9438,7 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
@@ -9462,10 +9449,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9491,16 +9478,16 @@
         <v>206</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9549,7 +9536,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9564,7 +9551,7 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>
